--- a/scripts/productos-digitales/guia-pasteleria/build/carta-de-apertura-y-escandallo.xlsx
+++ b/scripts/productos-digitales/guia-pasteleria/build/carta-de-apertura-y-escandallo.xlsx
@@ -1675,6 +1675,16 @@
         <f>SUM(B6:B8)</f>
         <v>2.5</v>
       </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>jornadas</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>suma de los tres perfiles</t>
+        </is>
+      </c>
       <c r="F9" s="15">
         <f>SUM(F6:F8)</f>
         <v>67850.14950000001</v>
@@ -1940,12 +1950,12 @@
       </c>
       <c r="D24" s="17" t="inlineStr">
         <is>
-          <t>PS-55 + PS-56</t>
+          <t>PS-56</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Éste es el ÚNICO número de margen que se teclea. La banda del sector es 30-35 % de food cost, que es exactamente lo mismo que decir 65-70 % de margen bruto.</t>
+          <t>Éste es el ÚNICO número de margen que se teclea. La banda del sector es 30-35 % de food cost SOBRE EL PRECIO DE VENTA (PS-56), que equivale a un margen bruto del 65-70 % sobre ese mismo precio de venta. Cuidado con las fuentes que dan el margen SOBRE COSTE: PS-55 publica ese mismo 65-70 % sobre coste, y eso es un food cost del 59-61 %, mucho más flojo. Antes de comparar tu margen con el de nadie, pregunta sobre qué base está calculado.</t>
         </is>
       </c>
     </row>
